--- a/result/variance_decomposition.xlsx
+++ b/result/variance_decomposition.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjyan\Desktop\ppt\ppt-2026年\文章素材\文章正文\scGEM_benchmark\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjyan\Documents\GitHub\scGEM_benchmark_NCS\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4303E0A2-5882-420C-B735-2E00414478D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C2A9BC-DFF9-4A54-BAEF-18076EA81F00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1155" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARI_variance" sheetId="1" r:id="rId1"/>
     <sheet name="NMI_variance" sheetId="2" r:id="rId2"/>
     <sheet name="Accuracy_variance" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -148,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -170,6 +183,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,176 +508,177 @@
     <col min="3" max="3" width="6.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
-        <v>9.67</v>
-      </c>
-      <c r="C2" s="3">
-        <v>58.37</v>
-      </c>
-      <c r="D2" s="3">
-        <v>3.62</v>
-      </c>
-      <c r="E2" s="3">
-        <v>28.34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="9">
+        <v>9.3689136856170201</v>
+      </c>
+      <c r="C2" s="9">
+        <v>58.384801537909802</v>
+      </c>
+      <c r="D2" s="9">
+        <v>4.0708689176003903</v>
+      </c>
+      <c r="E2" s="9">
+        <v>28.1754158588728</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C3" s="3">
-        <v>40.93</v>
-      </c>
-      <c r="D3" s="3">
-        <v>20.8</v>
-      </c>
-      <c r="E3" s="3">
-        <v>37.319999999999993</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="9">
+        <v>1.14181013057412</v>
+      </c>
+      <c r="C3" s="9">
+        <v>41.014810010239103</v>
+      </c>
+      <c r="D3" s="9">
+        <v>20.143633752121499</v>
+      </c>
+      <c r="E3" s="9">
+        <v>37.699746107065302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3">
-        <v>3.92</v>
-      </c>
-      <c r="C4" s="3">
-        <v>86.25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="3">
-        <v>9.4299999999999979</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="9">
+        <v>0.40459520156398798</v>
+      </c>
+      <c r="C4" s="9">
+        <v>95.776719430560505</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.76272055358698798</v>
+      </c>
+      <c r="E4" s="9">
+        <v>3.0559648142884601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3">
-        <v>3.57</v>
-      </c>
-      <c r="C5" s="3">
-        <v>38.479999999999997</v>
-      </c>
-      <c r="D5" s="3">
-        <v>16.55</v>
-      </c>
-      <c r="E5" s="3">
-        <v>41.400000000000013</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="9">
+        <v>5.5034316258290001</v>
+      </c>
+      <c r="C5" s="9">
+        <v>38.260271797972202</v>
+      </c>
+      <c r="D5" s="9">
+        <v>24.016676588625799</v>
+      </c>
+      <c r="E5" s="9">
+        <v>32.219619987573097</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3">
-        <v>1.56</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="E6" s="3">
-        <v>95.69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="9">
+        <v>3.5397143762182899</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0.44756480568733498</v>
+      </c>
+      <c r="D6" s="9">
+        <v>22.833652801715399</v>
+      </c>
+      <c r="E6" s="9">
+        <v>73.179068016379006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3">
-        <v>2.42</v>
-      </c>
-      <c r="C7" s="3">
-        <v>43.13</v>
-      </c>
-      <c r="D7" s="3">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="E7" s="3">
-        <v>14.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="9">
+        <v>1.41621073474773</v>
+      </c>
+      <c r="C7" s="9">
+        <v>43.012850917270903</v>
+      </c>
+      <c r="D7" s="9">
+        <v>28.767433233804599</v>
+      </c>
+      <c r="E7" s="9">
+        <v>26.803505114176801</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3">
-        <v>12.09</v>
-      </c>
-      <c r="C8" s="3">
-        <v>25.76</v>
-      </c>
-      <c r="D8" s="3">
-        <v>14.96</v>
-      </c>
-      <c r="E8" s="3">
-        <v>47.189999999999991</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="9">
+        <v>10.8902671282813</v>
+      </c>
+      <c r="C8" s="9">
+        <v>30.312652698086801</v>
+      </c>
+      <c r="D8" s="9">
+        <v>12.707328196219001</v>
+      </c>
+      <c r="E8" s="9">
+        <v>46.089751977412902</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3">
-        <v>0.82</v>
-      </c>
-      <c r="C9" s="3">
-        <v>62.41</v>
-      </c>
-      <c r="D9" s="3">
-        <v>12.63</v>
-      </c>
-      <c r="E9" s="3">
-        <v>24.140000000000011</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="9">
+        <v>0.80444581253451697</v>
+      </c>
+      <c r="C9" s="9">
+        <v>62.606647908829501</v>
+      </c>
+      <c r="D9" s="9">
+        <v>12.5329759340993</v>
+      </c>
+      <c r="E9" s="9">
+        <v>24.055930344536701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3">
-        <v>14.43</v>
-      </c>
-      <c r="C10" s="3">
-        <v>20.56</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1.44</v>
-      </c>
-      <c r="E10" s="3">
-        <v>63.569999999999993</v>
+      <c r="B10" s="9">
+        <v>11.122772076139899</v>
+      </c>
+      <c r="C10" s="9">
+        <v>18.816112459565399</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.5368177417383699</v>
+      </c>
+      <c r="E10" s="9">
+        <v>68.524297722556298</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CDE057F-D71A-4D94-A02F-3B278FE58EE5}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
@@ -673,7 +699,7 @@
     <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -690,7 +716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -707,7 +733,7 @@
         <v>23.27</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -724,7 +750,7 @@
         <v>36.180000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -741,7 +767,7 @@
         <v>3.2199999999999971</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -758,7 +784,7 @@
         <v>26.409999999999989</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
@@ -775,7 +801,7 @@
         <v>54.889999999999993</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -792,7 +818,7 @@
         <v>22.89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -809,7 +835,7 @@
         <v>37.956204379562053</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -826,7 +852,7 @@
         <v>23.052305230523039</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -842,6 +868,60 @@
       <c r="E10" s="5">
         <v>66.61</v>
       </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -856,24 +936,24 @@
   <cols>
     <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -881,85 +961,85 @@
       <c r="A2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="7">
-        <v>55.6</v>
-      </c>
-      <c r="C2" s="7">
-        <v>2.36</v>
-      </c>
-      <c r="D2" s="7">
-        <v>15.4</v>
-      </c>
-      <c r="E2" s="7">
-        <v>26.64</v>
+      <c r="B2" s="10">
+        <v>56.187689426776053</v>
+      </c>
+      <c r="C2" s="10">
+        <v>4.6929210344894203</v>
+      </c>
+      <c r="D2" s="10">
+        <v>12.172110619229164</v>
+      </c>
+      <c r="E2" s="10">
+        <v>26.947278919505351</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="7">
-        <v>75.319999999999993</v>
-      </c>
-      <c r="C3" s="7">
-        <v>1.24</v>
-      </c>
-      <c r="D3" s="7">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="E3" s="7">
-        <v>14.24</v>
+      <c r="B3" s="10">
+        <v>75.319556538622251</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1.2411996462375767</v>
+      </c>
+      <c r="D3" s="10">
+        <v>9.1998545149901716</v>
+      </c>
+      <c r="E3" s="10">
+        <v>14.239389300149982</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="7">
-        <v>12.19</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0.08</v>
-      </c>
-      <c r="D4" s="7">
-        <v>3.81</v>
-      </c>
-      <c r="E4" s="7">
-        <v>83.91</v>
+      <c r="B4" s="10">
+        <v>12.193351907758828</v>
+      </c>
+      <c r="C4" s="10">
+        <v>8.1992143264163458E-2</v>
+      </c>
+      <c r="D4" s="10">
+        <v>3.8118889344586426</v>
+      </c>
+      <c r="E4" s="10">
+        <v>83.91276701451838</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7">
-        <v>0.02</v>
-      </c>
-      <c r="C5" s="7">
-        <v>14.75</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E5" s="7">
-        <v>84.95</v>
+      <c r="B5" s="10">
+        <v>0.11496215999846834</v>
+      </c>
+      <c r="C5" s="10">
+        <v>15.778941612890199</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.24153718817498834</v>
+      </c>
+      <c r="E5" s="10">
+        <v>83.864559038936349</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="7">
-        <v>70.37</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="D6" s="7">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="E6" s="7">
-        <v>25.08</v>
+      <c r="B6" s="10">
+        <v>70.374344258637294</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.19457026610380079</v>
+      </c>
+      <c r="D6" s="10">
+        <v>4.3474981968853594</v>
+      </c>
+      <c r="E6" s="10">
+        <v>25.083587278373543</v>
       </c>
     </row>
   </sheetData>
